--- a/artfynd/A 37716-2025 artfynd.xlsx
+++ b/artfynd/A 37716-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136900431</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37716-2025 artfynd.xlsx
+++ b/artfynd/A 37716-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136900431</v>
       </c>
       <c r="B2" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37716-2025 artfynd.xlsx
+++ b/artfynd/A 37716-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136900431</v>
       </c>
       <c r="B2" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37716-2025 artfynd.xlsx
+++ b/artfynd/A 37716-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136900431</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37716-2025 artfynd.xlsx
+++ b/artfynd/A 37716-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136900431</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37716-2025 artfynd.xlsx
+++ b/artfynd/A 37716-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136900431</v>
       </c>
       <c r="B2" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37716-2025 artfynd.xlsx
+++ b/artfynd/A 37716-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136900431</v>
       </c>
       <c r="B2" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37716-2025 artfynd.xlsx
+++ b/artfynd/A 37716-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136900431</v>
       </c>
       <c r="B2" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37716-2025 artfynd.xlsx
+++ b/artfynd/A 37716-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136900431</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37716-2025 artfynd.xlsx
+++ b/artfynd/A 37716-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136900431</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37716-2025 artfynd.xlsx
+++ b/artfynd/A 37716-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136900431</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37716-2025 artfynd.xlsx
+++ b/artfynd/A 37716-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136900431</v>
       </c>
       <c r="B2" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37716-2025 artfynd.xlsx
+++ b/artfynd/A 37716-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136900431</v>
       </c>
       <c r="B2" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37716-2025 artfynd.xlsx
+++ b/artfynd/A 37716-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136900431</v>
       </c>
       <c r="B2" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37716-2025 artfynd.xlsx
+++ b/artfynd/A 37716-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136900431</v>
       </c>
       <c r="B2" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,9 +798,120 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137437914</v>
+      </c>
+      <c r="B3" t="n">
+        <v>75610</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stora Svaltjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>461072</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6578085</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bjurtjärn</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Juno Katainen</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Juno Katainen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137437914</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37716-2025 artfynd.xlsx
+++ b/artfynd/A 37716-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136900431</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -905,6 +905,710 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137437914</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137445036</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>St. Svaltjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>461031</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6578075</v>
+      </c>
+      <c r="S4" t="n">
+        <v>9</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bjurtjärn</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hålhack</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137445036</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137445039</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>St. Svaltjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>461094</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6578029</v>
+      </c>
+      <c r="S5" t="n">
+        <v>9</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bjurtjärn</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137445039</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137445046</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>St. Svaltjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>461109</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6578123</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bjurtjärn</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I flykt</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137445046</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137445048</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>St. Svaltjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>461131</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6578164</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bjurtjärn</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137445048</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137445034</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>St. Svaltjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>461022</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6578122</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bjurtjärn</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hack Se bilder</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137445034</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137445055</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>St. Svaltjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>461273</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6578140</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bjurtjärn</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Färska och äldre hack , rinner kåda från vissa hack. Lite hack på tallar runt om.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137445055</t>
         </is>
       </c>
     </row>
@@ -912,6 +1616,12 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37716-2025 artfynd.xlsx
+++ b/artfynd/A 37716-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136900431</v>
       </c>
       <c r="B2" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37716-2025 artfynd.xlsx
+++ b/artfynd/A 37716-2025 artfynd.xlsx
@@ -1526,6 +1526,10 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>St. Svaltjärnen, Vrm</t>
@@ -1602,7 +1606,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jesper Granback, Jens Johansen, Juno Katainen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 37716-2025 artfynd.xlsx
+++ b/artfynd/A 37716-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137437914</v>
       </c>
       <c r="B3" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>137445036</v>
       </c>
       <c r="B4" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>137445039</v>
       </c>
       <c r="B5" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>137445046</v>
       </c>
       <c r="B6" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>137445048</v>
       </c>
       <c r="B7" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>137445034</v>
       </c>
       <c r="B8" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>137445055</v>
       </c>
       <c r="B9" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
